--- a/artfynd/A 7747-2021 artfynd.xlsx
+++ b/artfynd/A 7747-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118603915</v>
+        <v>118603863</v>
       </c>
       <c r="B2" t="n">
         <v>57200</v>
@@ -710,19 +710,23 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581757</v>
+        <v>581641</v>
       </c>
       <c r="R2" t="n">
-        <v>6325951</v>
+        <v>6326235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118603863</v>
+        <v>118603915</v>
       </c>
       <c r="B3" t="n">
         <v>57200</v>
@@ -816,23 +820,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581641</v>
+        <v>581757</v>
       </c>
       <c r="R3" t="n">
-        <v>6326235</v>
+        <v>6325951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7747-2021 artfynd.xlsx
+++ b/artfynd/A 7747-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118603863</v>
+        <v>118603915</v>
       </c>
       <c r="B2" t="n">
         <v>57200</v>
@@ -710,23 +710,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581641</v>
+        <v>581757</v>
       </c>
       <c r="R2" t="n">
-        <v>6326235</v>
+        <v>6325951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118603915</v>
+        <v>118603863</v>
       </c>
       <c r="B3" t="n">
         <v>57200</v>
@@ -820,19 +816,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581757</v>
+        <v>581641</v>
       </c>
       <c r="R3" t="n">
-        <v>6325951</v>
+        <v>6326235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
